--- a/research/traditional_assets/database/data/kenya/kenya_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0916</v>
+        <v>-0.04484</v>
       </c>
       <c r="E2">
-        <v>-0.113</v>
+        <v>-0.0663</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.08223938223938224</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.08223938223938224</v>
       </c>
       <c r="I2">
-        <v>0.07782426778242678</v>
+        <v>0.07220077220077221</v>
       </c>
       <c r="J2">
-        <v>0.06873828451882845</v>
+        <v>0.05876987586665007</v>
       </c>
       <c r="K2">
-        <v>-14.06</v>
+        <v>-2.04</v>
       </c>
       <c r="L2">
-        <v>-0.5882845188284518</v>
+        <v>-0.07876447876447877</v>
       </c>
       <c r="M2">
-        <v>1.3585</v>
+        <v>0.906</v>
       </c>
       <c r="N2">
-        <v>0.04299050632911392</v>
+        <v>0.03737623762376237</v>
       </c>
       <c r="O2">
-        <v>-0.09662162162162163</v>
+        <v>-0.4441176470588236</v>
       </c>
       <c r="P2">
-        <v>1.3585</v>
+        <v>0.906</v>
       </c>
       <c r="Q2">
-        <v>0.04299050632911392</v>
+        <v>0.03737623762376237</v>
       </c>
       <c r="R2">
-        <v>-0.09662162162162163</v>
+        <v>-0.4441176470588236</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11</v>
+        <v>4.66</v>
       </c>
       <c r="V2">
-        <v>0.3481012658227848</v>
-      </c>
-      <c r="W2">
-        <v>-0.03903479125248509</v>
+        <v>0.1922442244224422</v>
       </c>
       <c r="X2">
-        <v>0.05293613607878555</v>
-      </c>
-      <c r="Y2">
-        <v>-0.09197092733127064</v>
+        <v>0.100283845491742</v>
       </c>
       <c r="Z2">
-        <v>0.1458117259471662</v>
-      </c>
-      <c r="AA2">
-        <v>0.04291661649608669</v>
+        <v>0.2337756115172849</v>
       </c>
       <c r="AB2">
-        <v>0.04547693396143332</v>
-      </c>
-      <c r="AC2">
-        <v>-0.002560317465346629</v>
+        <v>0.08027749872169306</v>
       </c>
       <c r="AD2">
-        <v>39.7</v>
+        <v>43.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>39.7</v>
+        <v>43.4</v>
       </c>
       <c r="AG2">
-        <v>28.7</v>
+        <v>38.73999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5568022440392706</v>
+        <v>0.641632170313424</v>
       </c>
       <c r="AI2">
-        <v>0.2874728457639392</v>
+        <v>0.3881932021466905</v>
       </c>
       <c r="AJ2">
-        <v>0.4759535655058043</v>
+        <v>0.6151159098126389</v>
       </c>
       <c r="AK2">
-        <v>0.2258064516129032</v>
+        <v>0.3615829755460145</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>20.3755868544601</v>
+      </c>
+      <c r="AP2">
+        <v>18.18779342723004</v>
       </c>
     </row>
     <row r="3">
@@ -710,46 +704,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.04019999999999999</v>
+        <v>0.00292</v>
       </c>
       <c r="E3">
-        <v>-0.113</v>
+        <v>-0.0663</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3435483870967742</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3435483870967742</v>
       </c>
       <c r="I3">
-        <v>0.3206896551724138</v>
+        <v>0.3016129032258065</v>
       </c>
       <c r="J3">
-        <v>0.2458086206896552</v>
+        <v>0.1893999306278183</v>
       </c>
       <c r="K3">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="L3">
-        <v>0.2655172413793104</v>
+        <v>0.1854838709677419</v>
       </c>
       <c r="M3">
-        <v>1.2975</v>
+        <v>0.906</v>
       </c>
       <c r="N3">
-        <v>0.0709016393442623</v>
+        <v>0.06335664335664336</v>
       </c>
       <c r="O3">
-        <v>0.8425324675324676</v>
+        <v>0.7878260869565218</v>
       </c>
       <c r="P3">
-        <v>1.2975</v>
+        <v>0.906</v>
       </c>
       <c r="Q3">
-        <v>0.0709016393442623</v>
+        <v>0.06335664335664336</v>
       </c>
       <c r="R3">
-        <v>0.8425324675324676</v>
+        <v>0.7878260869565218</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +752,16 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.2016393442622951</v>
-      </c>
-      <c r="W3">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.03360415921485008</v>
-      </c>
-      <c r="Y3">
-        <v>0.04339584078514992</v>
-      </c>
-      <c r="Z3">
-        <v>0.3491872366044552</v>
-      </c>
-      <c r="AA3">
-        <v>0.08583323299217338</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="AB3">
-        <v>0.03360415921485008</v>
-      </c>
-      <c r="AC3">
-        <v>0.0522290737773233</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,24 +773,24 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
       <c r="AJ3">
-        <v>-0.2525667351129363</v>
-      </c>
-      <c r="AK3">
-        <v>-0.2262415695892091</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
         <v>0</v>
       </c>
     </row>
@@ -832,7 +811,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.143</v>
+        <v>-0.0926</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,85 +826,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-15.6</v>
+        <v>-3.19</v>
       </c>
       <c r="L4">
-        <v>-0.8618784530386739</v>
+        <v>-0.1619289340101523</v>
       </c>
       <c r="M4">
-        <v>0.061</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.004586466165413534</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.00391025641025641</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.061</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.004586466165413534</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.00391025641025641</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>7.31</v>
+        <v>4.66</v>
       </c>
       <c r="V4">
-        <v>0.5496240601503759</v>
+        <v>0.4688128772635815</v>
       </c>
       <c r="W4">
-        <v>-0.1550695825049702</v>
+        <v>-0.04068877551020408</v>
       </c>
       <c r="X4">
-        <v>0.07226811294272102</v>
+        <v>0.1374481754964997</v>
       </c>
       <c r="Y4">
-        <v>-0.2273376954476912</v>
+        <v>-0.1781369510067037</v>
       </c>
       <c r="Z4">
-        <v>0.1228784792939579</v>
+        <v>0.1778138821193248</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05734970870801656</v>
+        <v>0.09743548195640182</v>
       </c>
       <c r="AC4">
-        <v>-0.05734970870801656</v>
+        <v>-0.09743548195640182</v>
       </c>
       <c r="AD4">
-        <v>39.7</v>
+        <v>43.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>39.7</v>
+        <v>43.4</v>
       </c>
       <c r="AG4">
-        <v>32.39</v>
+        <v>38.73999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.749056603773585</v>
+        <v>0.8136482939632547</v>
       </c>
       <c r="AI4">
-        <v>0.336155800169348</v>
+        <v>0.3881932021466905</v>
       </c>
       <c r="AJ4">
-        <v>0.7089078572991903</v>
+        <v>0.7958093672966311</v>
       </c>
       <c r="AK4">
-        <v>0.2923549056774077</v>
+        <v>0.3615829755460145</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/kenya/kenya_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,92 +587,98 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.04484</v>
-      </c>
-      <c r="E2">
-        <v>-0.0663</v>
-      </c>
       <c r="G2">
-        <v>0.08223938223938224</v>
+        <v>0.2316017316017316</v>
       </c>
       <c r="H2">
-        <v>0.08223938223938224</v>
+        <v>0.2316017316017316</v>
       </c>
       <c r="I2">
-        <v>0.07220077220077221</v>
+        <v>0.2021645021645022</v>
       </c>
       <c r="J2">
-        <v>0.05876987586665007</v>
+        <v>0.1231623420000173</v>
       </c>
       <c r="K2">
-        <v>-2.04</v>
+        <v>0.306</v>
       </c>
       <c r="L2">
-        <v>-0.07876447876447877</v>
+        <v>0.06623376623376623</v>
       </c>
       <c r="M2">
-        <v>0.906</v>
+        <v>0.8270000000000001</v>
       </c>
       <c r="N2">
-        <v>0.03737623762376237</v>
+        <v>0.08294884653961886</v>
       </c>
       <c r="O2">
-        <v>-0.4441176470588236</v>
+        <v>2.702614379084967</v>
       </c>
       <c r="P2">
-        <v>0.906</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03737623762376237</v>
+        <v>0.08124373119358075</v>
       </c>
       <c r="R2">
-        <v>-0.4441176470588236</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.01700000000000002</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02055622732769046</v>
       </c>
       <c r="U2">
-        <v>4.66</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>0.1922442244224422</v>
+        <v>0.2587763289869608</v>
+      </c>
+      <c r="W2">
+        <v>0.01537688442211055</v>
       </c>
       <c r="X2">
-        <v>0.100283845491742</v>
+        <v>0.07258346848284913</v>
+      </c>
+      <c r="Y2">
+        <v>-0.05720658406073858</v>
       </c>
       <c r="Z2">
-        <v>0.2337756115172849</v>
+        <v>0.2850092535471931</v>
+      </c>
+      <c r="AA2">
+        <v>0.03510240715854906</v>
       </c>
       <c r="AB2">
-        <v>0.08027749872169306</v>
+        <v>0.07258346848284913</v>
+      </c>
+      <c r="AC2">
+        <v>-0.03748106132430008</v>
       </c>
       <c r="AD2">
-        <v>43.4</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>43.4</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>38.73999999999999</v>
+        <v>-2.58</v>
       </c>
       <c r="AH2">
-        <v>0.641632170313424</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.3881932021466905</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.6151159098126389</v>
+        <v>-0.3491204330175913</v>
       </c>
       <c r="AK2">
-        <v>0.3615829755460145</v>
+        <v>-0.2299465240641711</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -681,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>20.3755868544601</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>18.18779342723004</v>
+        <v>-2.388888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -703,65 +709,74 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.00292</v>
-      </c>
-      <c r="E3">
-        <v>-0.0663</v>
-      </c>
       <c r="G3">
-        <v>0.3435483870967742</v>
+        <v>0.2316017316017316</v>
       </c>
       <c r="H3">
-        <v>0.3435483870967742</v>
+        <v>0.2316017316017316</v>
       </c>
       <c r="I3">
-        <v>0.3016129032258065</v>
+        <v>0.2021645021645022</v>
       </c>
       <c r="J3">
-        <v>0.1893999306278183</v>
+        <v>0.1231623420000173</v>
       </c>
       <c r="K3">
-        <v>1.15</v>
+        <v>0.306</v>
       </c>
       <c r="L3">
-        <v>0.1854838709677419</v>
+        <v>0.06623376623376623</v>
       </c>
       <c r="M3">
-        <v>0.906</v>
+        <v>0.8270000000000001</v>
       </c>
       <c r="N3">
-        <v>0.06335664335664336</v>
+        <v>0.08294884653961886</v>
       </c>
       <c r="O3">
-        <v>0.7878260869565218</v>
+        <v>2.702614379084967</v>
       </c>
       <c r="P3">
-        <v>0.906</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.06335664335664336</v>
+        <v>0.08124373119358075</v>
       </c>
       <c r="R3">
-        <v>0.7878260869565218</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.01700000000000002</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.02055622732769046</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2587763289869608</v>
+      </c>
+      <c r="W3">
+        <v>0.01537688442211055</v>
       </c>
       <c r="X3">
-        <v>0.06311951548698429</v>
+        <v>0.07258346848284913</v>
+      </c>
+      <c r="Y3">
+        <v>-0.05720658406073858</v>
+      </c>
+      <c r="Z3">
+        <v>0.2850092535471931</v>
+      </c>
+      <c r="AA3">
+        <v>0.03510240715854906</v>
       </c>
       <c r="AB3">
-        <v>0.06311951548698429</v>
+        <v>0.07258346848284913</v>
+      </c>
+      <c r="AC3">
+        <v>-0.03748106132430008</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -773,13 +788,19 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-2.58</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.3491204330175913</v>
+      </c>
+      <c r="AK3">
+        <v>-0.2299465240641711</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -791,123 +812,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HF Group Plc (NASE:HFCK)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.0926</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>-3.19</v>
-      </c>
-      <c r="L4">
-        <v>-0.1619289340101523</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>4.66</v>
-      </c>
-      <c r="V4">
-        <v>0.4688128772635815</v>
-      </c>
-      <c r="W4">
-        <v>-0.04068877551020408</v>
-      </c>
-      <c r="X4">
-        <v>0.1374481754964997</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1781369510067037</v>
-      </c>
-      <c r="Z4">
-        <v>0.1778138821193248</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.09743548195640182</v>
-      </c>
-      <c r="AC4">
-        <v>-0.09743548195640182</v>
-      </c>
-      <c r="AD4">
-        <v>43.4</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>43.4</v>
-      </c>
-      <c r="AG4">
-        <v>38.73999999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.8136482939632547</v>
-      </c>
-      <c r="AI4">
-        <v>0.3881932021466905</v>
-      </c>
-      <c r="AJ4">
-        <v>0.7958093672966311</v>
-      </c>
-      <c r="AK4">
-        <v>0.3615829755460145</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
+        <v>-2.388888888888889</v>
       </c>
     </row>
   </sheetData>
